--- a/artfynd/A 53603-2024 artfynd.xlsx
+++ b/artfynd/A 53603-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135593455</v>
       </c>
       <c r="B3" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53603-2024 artfynd.xlsx
+++ b/artfynd/A 53603-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135593455</v>
       </c>
       <c r="B3" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53603-2024 artfynd.xlsx
+++ b/artfynd/A 53603-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135593455</v>
       </c>
       <c r="B3" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53603-2024 artfynd.xlsx
+++ b/artfynd/A 53603-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593440</v>
       </c>
       <c r="B2" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135593455</v>
       </c>
       <c r="B3" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53603-2024 artfynd.xlsx
+++ b/artfynd/A 53603-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135593455</v>
       </c>
       <c r="B3" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53603-2024 artfynd.xlsx
+++ b/artfynd/A 53603-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135593455</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
